--- a/Resultados_6Sigma/Excel/Resultados_6Sigma.xlsx
+++ b/Resultados_6Sigma/Excel/Resultados_6Sigma.xlsx
@@ -14,6 +14,9 @@
     <sheet name="Comparacion" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Filas_detectadas" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Detalle_atipicos" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Correlacion_antes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Correlacion_despues" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Cambio_correlacion" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$1:$B$16</definedName>
@@ -23,6 +26,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Comparacion'!$A$1:$I$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Filas_detectadas'!$A$1:$O$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Detalle_atipicos'!$A$1:$M$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Correlacion_antes'!$A$1:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Correlacion_despues'!$A$1:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cambio_correlacion'!$A$1:$E$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -634,6 +640,1000 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Variable_1</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Variable_2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_antes</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_despues</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Cambio_r</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AcelX1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AcelY1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.04087072956304445</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.04088119609573129</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.046653268683972e-05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AcelX1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AcelZ1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.2545646333981131</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.254550602834036</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.403056407717207e-05</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AcelX1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GiroX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.00477797368457578</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.004789011970106509</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.103828553072894e-05</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AcelX1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GiroY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.008955888015581233</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.008956906524203962</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.018508622729203e-06</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AcelX1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GiroZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.006561738041395473</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.007071366071705241</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.0005096280303097675</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AcelX1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MagneX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.007990361762164323</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.00800927059979932</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.890883763499759e-05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AcelX1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MagneY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.007864020176112202</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.007891611717218396</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.759154110619326e-05</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AcelX1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MagneZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.00391847483467434</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.003910325815880815</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8.149018793524726e-06</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AcelX1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ter_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.05183562392438969</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.05186167410841377</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.605018402408038e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AcelY1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AcelZ1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.2277025921628899</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.2277082255984813</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5.633435591373415e-06</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AcelY1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GiroX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.009708355238884209</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.009709504308075366</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.149069191156912e-06</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AcelY1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GiroY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.004885509080865085</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.004898369148423385</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.286006755830005e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AcelY1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GiroZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.009230835279608921</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.01004512021534644</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.0008142849357375241</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AcelY1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MagneX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.01233987830115485</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.01235211552753473</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-1.22372263798888e-05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AcelY1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MagneY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.007285859108612893</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.007273543945657935</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-1.231516295495741e-05</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AcelY1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MagneZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.007378113978381393</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.007377337060067872</v>
+      </c>
+      <c r="E17" t="n">
+        <v>7.769183135207872e-07</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AcelY1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ter_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.0477608668004325</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.04775548813252205</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-5.378667910449497e-06</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AcelZ1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>GiroX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.003071249137912558</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.00308779298248905</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-1.654384457649202e-05</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AcelZ1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>GiroY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.007466736280121701</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.007477831471482752</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-1.109519136105117e-05</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AcelZ1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>GiroZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.01054171391961316</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.01138189772734293</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.0008401838077297715</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AcelZ1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MagneX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.001593103484744808</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.001619061857182505</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.595837243769719e-05</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AcelZ1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MagneY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.0009758718894268264</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.0009666430493178948</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-9.228840108931546e-06</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AcelZ1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MagneZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.003810133601607502</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.003809594008759023</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-5.395928484789973e-07</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AcelZ1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ter_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.02620646067935456</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.02621138303680919</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-4.922357454636289e-06</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>GiroX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GiroY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.0806278813221447</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.08066641260858301</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-3.853128643831194e-05</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>GiroX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>GiroZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.09304246128098234</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.09532226758663935</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.002279806305657009</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GiroX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MagneX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.01740997046063816</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.0173782296581181</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.174080252006314e-05</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>GiroX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MagneY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.01449573339325661</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.01449180258786511</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-3.930805391499231e-06</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>GiroX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MagneZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.01524154458350142</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-0.01520725402701846</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3.429055648295626e-05</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>GiroX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ter_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.09454454829853369</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.09453496427215566</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-9.584026378031685e-06</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>GiroY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>GiroZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.3078804023393233</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.317585250588763</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.009704848249439624</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>GiroY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MagneX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.01757606996989562</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.0175467713950038</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.929857489182217e-05</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>GiroY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MagneY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.008517271099585758</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.008501284182315803</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-1.598691726995526e-05</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>GiroY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MagneZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.008045282248889264</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-0.008044078090832209</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.204158057054733e-06</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>GiroY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ter_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.1131453034670798</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.1131580368837904</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.273341671062522e-05</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>GiroZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MagneX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.02450610766771297</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.02417265906463119</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.0003334486030817756</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>GiroZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MagneY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.02368587329298586</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-0.02456977106424998</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.0008838977712641201</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>GiroZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MagneZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.01955989746249828</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.0206291512635424</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.001069253801044123</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>GiroZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Ter_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.1558248166301081</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.1617251769666364</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-0.005900360336528326</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MagneX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MagneY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.002138424228931814</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-0.002141390545983007</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-2.966317051192671e-06</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MagneX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>MagneZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.006101326369885353</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-0.006107185601662909</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-5.859231777555901e-06</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MagneX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Ter_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.1109764180991061</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-0.1109731090181468</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3.309080959329469e-06</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MagneY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>MagneZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.02760583949293359</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-0.02762193698401487</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-1.609749108127598e-05</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MagneY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ter_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.08379430406297174</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.08380494425135231</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.064018838056735e-05</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MagneZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Ter_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.06902684908260795</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-0.06901349737145496</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.335171115299238e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E46"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3121,4 +4121,914 @@
   <autoFilter ref="A1:M7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>AcelX1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>AcelY1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>AcelZ1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>GiroX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>GiroY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>GiroZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>MagneX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>MagneY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MagneZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Ter_SisGenEol</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AcelX1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.9999999999999998</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.04087072956304445</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.2545646333981131</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.00477797368457578</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.008955888015581233</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.006561738041395473</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.007990361762164323</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.007864020176112202</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.00391847483467434</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.05183562392438969</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AcelY1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.04087072956304445</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2277025921628899</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.009708355238884209</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.004885509080865085</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.009230835279608921</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.01233987830115485</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.007285859108612893</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0.007378113978381393</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0477608668004325</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AcelZ1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.2545646333981131</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.2277025921628899</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.003071249137912558</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.007466736280121701</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01054171391961316</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.001593103484744808</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0009758718894268264</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.003810133601607502</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.02620646067935456</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GiroX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.00477797368457578</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.009708355238884209</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.003071249137912558</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.0806278813221447</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.09304246128098234</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.01740997046063816</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.01449573339325661</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.01524154458350142</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.09454454829853369</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GiroY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.008955888015581233</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.004885509080865085</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.007466736280121701</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.0806278813221447</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.3078804023393233</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.01757606996989562</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.008517271099585758</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.008045282248889264</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.1131453034670798</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GiroZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.006561738041395473</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.009230835279608919</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.01054171391961316</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.09304246128098234</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.3078804023393233</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.02450610766771297</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.02368587329298586</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.01955989746249828</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.1558248166301081</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MagneX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.007990361762164323</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.01233987830115485</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.001593103484744808</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.01740997046063816</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.01757606996989562</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.02450610766771297</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.002138424228931814</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.006101326369885353</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.1109764180991061</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MagneY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.007864020176112202</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.007285859108612893</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0009758718894268264</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01449573339325661</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.008517271099585758</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.02368587329298586</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.002138424228931814</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.02760583949293359</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.08379430406297174</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MagneZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.003918474834674339</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.007378113978381392</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.003810133601607502</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.01524154458350142</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.008045282248889264</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01955989746249828</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.006101326369885353</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.02760583949293359</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.06902684908260795</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ter_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.05183562392438969</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.0477608668004325</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.02620646067935456</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.09454454829853369</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1131453034670797</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.1558248166301081</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.1109764180991061</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.08379430406297173</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.06902684908260794</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>AcelX1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>AcelY1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>AcelZ1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>GiroX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>GiroY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>GiroZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>MagneX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>MagneY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MagneZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Ter_SisGenEol</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AcelX1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.04088119609573129</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.254550602834036</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.004789011970106509</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.008956906524203962</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.007071366071705241</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.00800927059979932</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.007891611717218396</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.003910325815880815</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.05186167410841377</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AcelY1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.04088119609573129</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2277082255984813</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.009709504308075366</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.004898369148423385</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.01004512021534644</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.01235211552753473</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.007273543945657935</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0.007377337060067872</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.04775548813252205</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AcelZ1_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.254550602834036</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.2277082255984813</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.00308779298248905</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.007477831471482752</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01138189772734293</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.001619061857182505</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0009666430493178948</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.003809594008759023</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.02621138303680919</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GiroX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.004789011970106508</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.009709504308075366</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.00308779298248905</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.08066641260858301</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.09532226758663935</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.0173782296581181</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.01449180258786511</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.01520725402701846</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.09453496427215566</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GiroY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.008956906524203964</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.004898369148423384</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.007477831471482752</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.08066641260858301</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.317585250588763</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.0175467713950038</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.008501284182315803</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.008044078090832209</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.1131580368837904</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GiroZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.007071366071705241</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.01004512021534645</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.01138189772734293</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.09532226758663935</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.317585250588763</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.02417265906463119</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.02456977106424998</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.0206291512635424</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.1617251769666364</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MagneX_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.00800927059979932</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.01235211552753473</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.001619061857182505</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.0173782296581181</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.0175467713950038</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0241726590646312</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9999999999999998</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.002141390545983007</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.006107185601662909</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.1109731090181468</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MagneY_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.007891611717218396</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.007273543945657935</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0009666430493178946</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01449180258786511</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.008501284182315803</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.02456977106424998</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.002141390545983007</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.02762193698401487</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.08380494425135231</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MagneZ_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.003910325815880815</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.007377337060067872</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.003809594008759024</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.01520725402701846</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.008044078090832211</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0206291512635424</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.006107185601662909</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.02762193698401487</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.9999999999999998</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.06901349737145496</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ter_SisGenEol</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.05186167410841377</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.04775548813252205</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.02621138303680919</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.09453496427215566</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1131580368837904</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.1617251769666364</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.1109731090181467</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.08380494425135231</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.06901349737145494</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.9999999999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>